--- a/physician_forms/014_toilet_training_checklist--physician_forms.xlsx
+++ b/physician_forms/014_toilet_training_checklist--physician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'male'}</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'female'}</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'not_started'}</t>
+          <t>not started</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'in_progress'}</t>
+          <t>in progress</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'abnormal'}</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'abnormal'}</t>
+          <t>abnormal</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'no_history'}</t>
+          <t>no_history</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'no_history'}</t>
+          <t>no history</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'history'}</t>
+          <t>history</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'not_applicable'}</t>
+          <t>not applicable</t>
         </is>
       </c>
     </row>
